--- a/business_surveys/023_facility_management_modernization_survey--business_surveys.xlsx
+++ b/business_surveys/023_facility_management_modernization_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'office_building'}</t>
+          <t>office_building</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Office Building'}</t>
+          <t>Office Building</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'asset_management'}</t>
+          <t>asset_management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Asset Management'}</t>
+          <t>Asset Management</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'energy_management'}</t>
+          <t>energy_management</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Energy Management'}</t>
+          <t>Energy Management</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'budget_constraints'}</t>
+          <t>budget_constraints</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Budget Constraints'}</t>
+          <t>Budget Constraints</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'limited_resources'}</t>
+          <t>limited_resources</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Limited Resources'}</t>
+          <t>Limited Resources</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'strategic'}</t>
+          <t>strategic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Strategic'}</t>
+          <t>Strategic</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tactical'}</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tactical'}</t>
+          <t>Tactical</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
